--- a/Soubhanik/checkupp_product_backlog_v2.xlsx
+++ b/Soubhanik/checkupp_product_backlog_v2.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Anodiam\2026\CheckUpp_Parent\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Anodiam\2026\CheckUpp_Parent\CheckUpp\Soubhanik\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8B0442D5-151B-4542-AF7D-7C69D2BCBB99}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E7E6CBC4-C450-45D8-8943-C8BC59286CBB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,14 +16,14 @@
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$I$1:$I$42</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$I$1:$I$43</definedName>
   </definedNames>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="293" uniqueCount="247">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="257" uniqueCount="210">
   <si>
     <t>Epic #</t>
   </si>
@@ -56,9 +56,6 @@
   </si>
   <si>
     <t>Onboarding</t>
-  </si>
-  <si>
-    <t>1.1</t>
   </si>
   <si>
     <t>new user</t>
@@ -78,9 +75,6 @@
     <t>Slide 1</t>
   </si>
   <si>
-    <t>1.2</t>
-  </si>
-  <si>
     <t>sign up with my details</t>
   </si>
   <si>
@@ -95,9 +89,6 @@
     <t>Slide 2</t>
   </si>
   <si>
-    <t>1.3</t>
-  </si>
-  <si>
     <t>registered user</t>
   </si>
   <si>
@@ -112,9 +103,6 @@
 - Successful login lands on Home Screen</t>
   </si>
   <si>
-    <t>1.4</t>
-  </si>
-  <si>
     <t>user who forgot their password</t>
   </si>
   <si>
@@ -135,9 +123,6 @@
     <t>Home Screen</t>
   </si>
   <si>
-    <t>2.1</t>
-  </si>
-  <si>
     <t>logged-in user</t>
   </si>
   <si>
@@ -155,9 +140,6 @@
     <t>Slide 4</t>
   </si>
   <si>
-    <t>2.2</t>
-  </si>
-  <si>
     <t>tap a health category tile on the home screen</t>
   </si>
   <si>
@@ -175,9 +157,6 @@
     <t>Your Health Overview</t>
   </si>
   <si>
-    <t>3.1</t>
-  </si>
-  <si>
     <t>see an interactive overview of all my health checks</t>
   </si>
   <si>
@@ -195,12 +174,6 @@
     <t>Discussion #12 – SOUBHANIK</t>
   </si>
   <si>
-    <t>3.2</t>
-  </si>
-  <si>
-    <t>tap a health check in the overview to see due vs completed tests</t>
-  </si>
-  <si>
     <t>I can manage upcoming health tasks</t>
   </si>
   <si>
@@ -212,9 +185,6 @@
     <t>Cancer Screenings</t>
   </si>
   <si>
-    <t>4.1</t>
-  </si>
-  <si>
     <t>user</t>
   </si>
   <si>
@@ -232,9 +202,6 @@
   </si>
   <si>
     <t>Discussion #5 – NATHAN</t>
-  </si>
-  <si>
-    <t>4.2</t>
   </si>
   <si>
     <t>toggle 'Never had a screening' on or off per cancer type</t>
@@ -248,9 +215,6 @@
 - 'Never had a screening' toggled on/off changes display</t>
   </si>
   <si>
-    <t>4.3</t>
-  </si>
-  <si>
     <t>user who has completed a cancer screening</t>
   </si>
   <si>
@@ -271,9 +235,6 @@
     <t>Discussion #7 – NATHAN</t>
   </si>
   <si>
-    <t>4.4</t>
-  </si>
-  <si>
     <t>user viewing a cancer screening result</t>
   </si>
   <si>
@@ -288,9 +249,6 @@
   </si>
   <si>
     <t>Discussion #6 – NATHAN</t>
-  </si>
-  <si>
-    <t>4.5</t>
   </si>
   <si>
     <t>female user</t>
@@ -313,9 +271,6 @@
     <t>Immunisation</t>
   </si>
   <si>
-    <t>5.1</t>
-  </si>
-  <si>
     <t>view my immunisation history and upcoming vaccinations</t>
   </si>
   <si>
@@ -333,9 +288,6 @@
     <t>Discussion #13 – SOUBHANIK</t>
   </si>
   <si>
-    <t>5.2</t>
-  </si>
-  <si>
     <t>see vaccination schedules by category (children, 50+, 65+, 70+, pregnancy, travel)</t>
   </si>
   <si>
@@ -353,9 +305,6 @@
     <t>Pregnancy</t>
   </si>
   <si>
-    <t>6.1</t>
-  </si>
-  <si>
     <t>pregnant user</t>
   </si>
   <si>
@@ -376,9 +325,6 @@
     <t>Discussion #8 – TANVI; User Journey: Mia (32yo, 10wks)</t>
   </si>
   <si>
-    <t>6.2</t>
-  </si>
-  <si>
     <t>female user aged 40–60</t>
   </si>
   <si>
@@ -398,9 +344,6 @@
     <t>Document Wallet</t>
   </si>
   <si>
-    <t>7.1</t>
-  </si>
-  <si>
     <t>store health documents locally or in a cloud service I choose</t>
   </si>
   <si>
@@ -417,9 +360,6 @@
     <t>Discussion #10 – NATHAN</t>
   </si>
   <si>
-    <t>7.2</t>
-  </si>
-  <si>
     <t>store insurance, Medicare, and identity documents securely</t>
   </si>
   <si>
@@ -434,9 +374,6 @@
   </si>
   <si>
     <t>e-Script</t>
-  </si>
-  <si>
-    <t>8.1</t>
   </si>
   <si>
     <t>signed-in user</t>
@@ -457,9 +394,6 @@
   </si>
   <si>
     <t>Discussion #11 – NATHAN; per wireframe user story</t>
-  </si>
-  <si>
-    <t>8.2</t>
   </si>
   <si>
     <t>display my e-Script as a QR code and share it via native share sheet</t>
@@ -480,9 +414,6 @@
     <t>Profile</t>
   </si>
   <si>
-    <t>9.1</t>
-  </si>
-  <si>
     <t>view and edit my profile information</t>
   </si>
   <si>
@@ -500,9 +431,6 @@
     <t>Health Checks Hub</t>
   </si>
   <si>
-    <t>10.1</t>
-  </si>
-  <si>
     <t>see a list of all available health checks</t>
   </si>
   <si>
@@ -514,9 +442,6 @@
   </si>
   <si>
     <t>Slide 16</t>
-  </si>
-  <si>
-    <t>10.2</t>
   </si>
   <si>
     <t>user who has completed a health check</t>
@@ -533,9 +458,6 @@
 - Result entry screens shown in subsequent slides</t>
   </si>
   <si>
-    <t>10.3</t>
-  </si>
-  <si>
     <t>user who has not completed a health check</t>
   </si>
   <si>
@@ -553,9 +475,6 @@
   </si>
   <si>
     <t>Vision Check</t>
-  </si>
-  <si>
-    <t>11.1</t>
   </si>
   <si>
     <t>log my vision check results</t>
@@ -575,9 +494,6 @@
     <t>Dental Health Check</t>
   </si>
   <si>
-    <t>12.1</t>
-  </si>
-  <si>
     <t>log my dental health check results</t>
   </si>
   <si>
@@ -595,9 +511,6 @@
     <t>Mental Health Check</t>
   </si>
   <si>
-    <t>13.1</t>
-  </si>
-  <si>
     <t>complete the K-10 and DASS-21 mental health assessments</t>
   </si>
   <si>
@@ -613,9 +526,6 @@
   </si>
   <si>
     <t>Discussion #16 – SOUBHANIK</t>
-  </si>
-  <si>
-    <t>13.2</t>
   </si>
   <si>
     <t>track sleep quality/quantity, exercise, and symptoms and add free-text notes</t>
@@ -633,9 +543,6 @@
     <t>Cardiovascular &amp; Diabetes Health Check</t>
   </si>
   <si>
-    <t>14.1</t>
-  </si>
-  <si>
     <t>log my cardiovascular health check measurements (BP, cholesterol etc.)</t>
   </si>
   <si>
@@ -653,9 +560,6 @@
     <t>Discussion #1 – SOUBHANIK</t>
   </si>
   <si>
-    <t>14.2</t>
-  </si>
-  <si>
     <t>capture a photo of my cardio test results and have the data extracted</t>
   </si>
   <si>
@@ -667,9 +571,6 @@
 - User confirms/edits before saving</t>
   </si>
   <si>
-    <t>14.3</t>
-  </si>
-  <si>
     <t>user entering cardiovascular data</t>
   </si>
   <si>
@@ -690,9 +591,6 @@
     <t>Discussion #2 – SOUBHANIK</t>
   </si>
   <si>
-    <t>14.4</t>
-  </si>
-  <si>
     <t>log my diabetes health check results (HbA1c, blood sugar etc.)</t>
   </si>
   <si>
@@ -710,9 +608,6 @@
     <t>Screenings Schedule</t>
   </si>
   <si>
-    <t>15.1</t>
-  </si>
-  <si>
     <t>view my upcoming and overdue screenings in a schedule view</t>
   </si>
   <si>
@@ -730,9 +625,6 @@
     <t>Discussion #9 – TANVI</t>
   </si>
   <si>
-    <t>15.2</t>
-  </si>
-  <si>
     <t>sync health check appointments to my device calendar</t>
   </si>
   <si>
@@ -747,9 +639,6 @@
     <t>AI &amp; Recommendations (No wireframe)</t>
   </si>
   <si>
-    <t>16.1</t>
-  </si>
-  <si>
     <t>receive AI-powered personalised health recommendations</t>
   </si>
   <si>
@@ -767,9 +656,6 @@
     <t>Discussion #14 – SAYAN, ANIRBAN; #18 AI explainability &amp; audit trail</t>
   </si>
   <si>
-    <t>16.2</t>
-  </si>
-  <si>
     <t>developer/admin</t>
   </si>
   <si>
@@ -784,9 +670,6 @@
   </si>
   <si>
     <t>Discussion #18 – SAYAN, ANIRBAN</t>
-  </si>
-  <si>
-    <t>16.3</t>
   </si>
   <si>
     <t>receive a Health Summary PDF</t>
@@ -801,9 +684,6 @@
   </si>
   <si>
     <t>Discussion #15 – ANIRBAN; JSON/XML format TBD</t>
-  </si>
-  <si>
-    <t>16.4</t>
   </si>
   <si>
     <t>have my data encrypted in-flight and at rest with secure auth</t>
@@ -819,9 +699,6 @@
   </si>
   <si>
     <t>Discussion #17; Medical app-grade security</t>
-  </si>
-  <si>
-    <t>16.5</t>
   </si>
   <si>
     <t>development team</t>
@@ -842,12 +719,26 @@
   <si>
     <t>Discussion #19</t>
   </si>
+  <si>
+    <t>tap a health check in the overview to see due, completed and rescheduled tests</t>
+  </si>
+  <si>
+    <t>tap a Quick Actions option (Cancer screenings, Health checkups, Immunization Checkups)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">I can see my appointment date, time, clinic name, address and doctor for the same </t>
+  </si>
+  <si>
+    <t>- Tapping opens detail view
+- Clearly displays appointment date and time, clinic name, clinic address, doctor name
+- Back navigation returns to Health Overview screen</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -885,6 +776,11 @@
     <font>
       <sz val="10"/>
       <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Calibri"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="15">
@@ -1067,7 +963,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="54">
+  <cellXfs count="56">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1148,15 +1044,9 @@
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="11" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="11" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="11" borderId="5" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="12" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="12" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1183,11 +1073,17 @@
     <xf numFmtId="0" fontId="5" fillId="14" borderId="5" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="11" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="12" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="10" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1218,6 +1114,12 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="6" fillId="7" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -1499,7 +1401,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:I68"/>
+  <dimension ref="A1:I69"/>
   <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="5.88671875" style="2" bestFit="1" customWidth="1"/>
@@ -1564,92 +1466,92 @@
       <c r="B3" s="42" t="s">
         <v>10</v>
       </c>
-      <c r="C3" s="14" t="s">
+      <c r="C3" s="14">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="D3" s="15" t="s">
         <v>11</v>
       </c>
-      <c r="D3" s="15" t="s">
+      <c r="E3" s="15" t="s">
         <v>12</v>
       </c>
-      <c r="E3" s="15" t="s">
+      <c r="F3" s="15" t="s">
         <v>13</v>
       </c>
-      <c r="F3" s="15" t="s">
+      <c r="G3" s="15" t="s">
         <v>14</v>
       </c>
-      <c r="G3" s="15" t="s">
+      <c r="H3" s="14" t="s">
         <v>15</v>
       </c>
-      <c r="H3" s="14" t="s">
+      <c r="I3" s="15"/>
+    </row>
+    <row r="4" spans="1:9" s="11" customFormat="1" ht="41.4" x14ac:dyDescent="0.3">
+      <c r="A4" s="40"/>
+      <c r="B4" s="40"/>
+      <c r="C4" s="14">
+        <v>1.2</v>
+      </c>
+      <c r="D4" s="15" t="s">
+        <v>11</v>
+      </c>
+      <c r="E4" s="15" t="s">
         <v>16</v>
       </c>
-      <c r="I3" s="15"/>
-    </row>
-    <row r="4" spans="1:9" s="11" customFormat="1" ht="41.4" x14ac:dyDescent="0.3">
-      <c r="A4" s="41"/>
-      <c r="B4" s="41"/>
-      <c r="C4" s="14" t="s">
+      <c r="F4" s="15" t="s">
         <v>17</v>
       </c>
-      <c r="D4" s="15" t="s">
-        <v>12</v>
-      </c>
-      <c r="E4" s="15" t="s">
+      <c r="G4" s="15" t="s">
         <v>18</v>
       </c>
-      <c r="F4" s="15" t="s">
+      <c r="H4" s="14" t="s">
         <v>19</v>
       </c>
-      <c r="G4" s="15" t="s">
+      <c r="I4" s="15"/>
+    </row>
+    <row r="5" spans="1:9" s="11" customFormat="1" ht="41.4" x14ac:dyDescent="0.3">
+      <c r="A5" s="40"/>
+      <c r="B5" s="40"/>
+      <c r="C5" s="14">
+        <v>1.3</v>
+      </c>
+      <c r="D5" s="15" t="s">
         <v>20</v>
       </c>
-      <c r="H4" s="14" t="s">
+      <c r="E5" s="15" t="s">
         <v>21</v>
       </c>
-      <c r="I4" s="15"/>
-    </row>
-    <row r="5" spans="1:9" s="11" customFormat="1" ht="41.4" x14ac:dyDescent="0.3">
-      <c r="A5" s="41"/>
-      <c r="B5" s="41"/>
-      <c r="C5" s="14" t="s">
+      <c r="F5" s="15" t="s">
         <v>22</v>
       </c>
-      <c r="D5" s="15" t="s">
+      <c r="G5" s="15" t="s">
         <v>23</v>
       </c>
-      <c r="E5" s="15" t="s">
+      <c r="H5" s="14" t="s">
+        <v>19</v>
+      </c>
+      <c r="I5" s="15"/>
+    </row>
+    <row r="6" spans="1:9" s="11" customFormat="1" ht="41.4" x14ac:dyDescent="0.3">
+      <c r="A6" s="41"/>
+      <c r="B6" s="41"/>
+      <c r="C6" s="14">
+        <v>1.4</v>
+      </c>
+      <c r="D6" s="15" t="s">
         <v>24</v>
       </c>
-      <c r="F5" s="15" t="s">
+      <c r="E6" s="15" t="s">
         <v>25</v>
       </c>
-      <c r="G5" s="15" t="s">
+      <c r="F6" s="15" t="s">
         <v>26</v>
       </c>
-      <c r="H5" s="14" t="s">
-        <v>21</v>
-      </c>
-      <c r="I5" s="15"/>
-    </row>
-    <row r="6" spans="1:9" s="11" customFormat="1" ht="41.4" x14ac:dyDescent="0.3">
-      <c r="A6" s="40"/>
-      <c r="B6" s="40"/>
-      <c r="C6" s="14" t="s">
+      <c r="G6" s="15" t="s">
         <v>27</v>
       </c>
-      <c r="D6" s="15" t="s">
+      <c r="H6" s="14" t="s">
         <v>28</v>
-      </c>
-      <c r="E6" s="15" t="s">
-        <v>29</v>
-      </c>
-      <c r="F6" s="15" t="s">
-        <v>30</v>
-      </c>
-      <c r="G6" s="15" t="s">
-        <v>31</v>
-      </c>
-      <c r="H6" s="14" t="s">
-        <v>32</v>
       </c>
       <c r="I6" s="15"/>
     </row>
@@ -1658,976 +1560,987 @@
         <v>2</v>
       </c>
       <c r="B7" s="43" t="s">
+        <v>29</v>
+      </c>
+      <c r="C7" s="17">
+        <v>2.1</v>
+      </c>
+      <c r="D7" s="18" t="s">
+        <v>30</v>
+      </c>
+      <c r="E7" s="18" t="s">
+        <v>31</v>
+      </c>
+      <c r="F7" s="18" t="s">
+        <v>32</v>
+      </c>
+      <c r="G7" s="18" t="s">
         <v>33</v>
       </c>
-      <c r="C7" s="17" t="s">
+      <c r="H7" s="17" t="s">
         <v>34</v>
       </c>
-      <c r="D7" s="18" t="s">
+      <c r="I7" s="18"/>
+    </row>
+    <row r="8" spans="1:9" s="11" customFormat="1" ht="41.4" x14ac:dyDescent="0.3">
+      <c r="A8" s="41"/>
+      <c r="B8" s="41"/>
+      <c r="C8" s="17">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="D8" s="18" t="s">
+        <v>30</v>
+      </c>
+      <c r="E8" s="18" t="s">
         <v>35</v>
       </c>
-      <c r="E7" s="18" t="s">
+      <c r="F8" s="18" t="s">
         <v>36</v>
       </c>
-      <c r="F7" s="18" t="s">
+      <c r="G8" s="18" t="s">
         <v>37</v>
       </c>
-      <c r="G7" s="18" t="s">
+      <c r="H8" s="17" t="s">
         <v>38</v>
       </c>
-      <c r="H7" s="17" t="s">
-        <v>39</v>
-      </c>
-      <c r="I7" s="18"/>
-    </row>
-    <row r="8" spans="1:9" s="11" customFormat="1" ht="41.4" x14ac:dyDescent="0.3">
-      <c r="A8" s="40"/>
-      <c r="B8" s="40"/>
-      <c r="C8" s="17" t="s">
-        <v>40</v>
-      </c>
-      <c r="D8" s="18" t="s">
-        <v>35</v>
-      </c>
-      <c r="E8" s="18" t="s">
-        <v>41</v>
-      </c>
-      <c r="F8" s="18" t="s">
-        <v>42</v>
-      </c>
-      <c r="G8" s="18" t="s">
-        <v>43</v>
-      </c>
-      <c r="H8" s="17" t="s">
-        <v>44</v>
-      </c>
       <c r="I8" s="18"/>
     </row>
-    <row r="9" spans="1:9" s="11" customFormat="1" ht="55.2" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:9" s="11" customFormat="1" ht="41.4" x14ac:dyDescent="0.3">
       <c r="A9" s="49">
         <v>3</v>
       </c>
       <c r="B9" s="49" t="s">
+        <v>39</v>
+      </c>
+      <c r="C9" s="19">
+        <v>3.1</v>
+      </c>
+      <c r="D9" s="20" t="s">
+        <v>30</v>
+      </c>
+      <c r="E9" s="20" t="s">
+        <v>40</v>
+      </c>
+      <c r="F9" s="20" t="s">
+        <v>41</v>
+      </c>
+      <c r="G9" s="20" t="s">
+        <v>42</v>
+      </c>
+      <c r="H9" s="19" t="s">
+        <v>43</v>
+      </c>
+      <c r="I9" s="20" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9" s="11" customFormat="1" ht="55.2" x14ac:dyDescent="0.3">
+      <c r="A10" s="54"/>
+      <c r="B10" s="54"/>
+      <c r="C10" s="19">
+        <v>3.2</v>
+      </c>
+      <c r="D10" s="20" t="s">
+        <v>30</v>
+      </c>
+      <c r="E10" s="20" t="s">
+        <v>207</v>
+      </c>
+      <c r="F10" s="20" t="s">
+        <v>208</v>
+      </c>
+      <c r="G10" s="55" t="s">
+        <v>209</v>
+      </c>
+      <c r="H10" s="19"/>
+      <c r="I10" s="20"/>
+    </row>
+    <row r="11" spans="1:9" s="11" customFormat="1" ht="41.4" x14ac:dyDescent="0.3">
+      <c r="A11" s="41"/>
+      <c r="B11" s="41"/>
+      <c r="C11" s="19">
+        <v>3.3</v>
+      </c>
+      <c r="D11" s="20" t="s">
+        <v>30</v>
+      </c>
+      <c r="E11" s="20" t="s">
+        <v>206</v>
+      </c>
+      <c r="F11" s="20" t="s">
         <v>45</v>
       </c>
-      <c r="C9" s="19" t="s">
+      <c r="G11" s="20" t="s">
         <v>46</v>
       </c>
-      <c r="D9" s="20" t="s">
-        <v>35</v>
-      </c>
-      <c r="E9" s="20" t="s">
+      <c r="H11" s="19" t="s">
+        <v>43</v>
+      </c>
+      <c r="I11" s="20" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9" s="11" customFormat="1" ht="41.4" x14ac:dyDescent="0.3">
+      <c r="A12" s="48">
+        <v>4</v>
+      </c>
+      <c r="B12" s="48" t="s">
         <v>47</v>
       </c>
-      <c r="F9" s="20" t="s">
+      <c r="C12" s="21">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="D12" s="22" t="s">
         <v>48</v>
       </c>
-      <c r="G9" s="20" t="s">
+      <c r="E12" s="22" t="s">
         <v>49</v>
       </c>
-      <c r="H9" s="19" t="s">
+      <c r="F12" s="22" t="s">
         <v>50</v>
       </c>
-      <c r="I9" s="20" t="s">
+      <c r="G12" s="22" t="s">
         <v>51</v>
       </c>
-    </row>
-    <row r="10" spans="1:9" s="11" customFormat="1" ht="41.4" x14ac:dyDescent="0.3">
-      <c r="A10" s="40"/>
-      <c r="B10" s="40"/>
-      <c r="C10" s="19" t="s">
+      <c r="H12" s="21" t="s">
         <v>52</v>
       </c>
-      <c r="D10" s="20" t="s">
-        <v>35</v>
-      </c>
-      <c r="E10" s="20" t="s">
+      <c r="I12" s="22" t="s">
         <v>53</v>
       </c>
-      <c r="F10" s="20" t="s">
+    </row>
+    <row r="13" spans="1:9" s="11" customFormat="1" ht="41.4" x14ac:dyDescent="0.3">
+      <c r="A13" s="40"/>
+      <c r="B13" s="40"/>
+      <c r="C13" s="21">
+        <v>4.2</v>
+      </c>
+      <c r="D13" s="22" t="s">
+        <v>48</v>
+      </c>
+      <c r="E13" s="22" t="s">
         <v>54</v>
       </c>
-      <c r="G10" s="20" t="s">
+      <c r="F13" s="22" t="s">
         <v>55</v>
       </c>
-      <c r="H10" s="19" t="s">
-        <v>50</v>
-      </c>
-      <c r="I10" s="20" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="11" spans="1:9" s="11" customFormat="1" ht="41.4" x14ac:dyDescent="0.3">
-      <c r="A11" s="48">
-        <v>4</v>
-      </c>
-      <c r="B11" s="48" t="s">
+      <c r="G13" s="22" t="s">
         <v>56</v>
       </c>
-      <c r="C11" s="21" t="s">
+      <c r="H13" s="21" t="s">
+        <v>52</v>
+      </c>
+      <c r="I13" s="22"/>
+    </row>
+    <row r="14" spans="1:9" s="11" customFormat="1" ht="41.4" x14ac:dyDescent="0.3">
+      <c r="A14" s="40"/>
+      <c r="B14" s="40"/>
+      <c r="C14" s="21">
+        <v>4.3</v>
+      </c>
+      <c r="D14" s="22" t="s">
         <v>57</v>
       </c>
-      <c r="D11" s="22" t="s">
+      <c r="E14" s="22" t="s">
         <v>58</v>
       </c>
-      <c r="E11" s="22" t="s">
+      <c r="F14" s="22" t="s">
         <v>59</v>
       </c>
-      <c r="F11" s="22" t="s">
+      <c r="G14" s="22" t="s">
         <v>60</v>
       </c>
-      <c r="G11" s="22" t="s">
+      <c r="H14" s="21" t="s">
         <v>61</v>
       </c>
-      <c r="H11" s="21" t="s">
+      <c r="I14" s="22" t="s">
         <v>62</v>
-      </c>
-      <c r="I11" s="22" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="12" spans="1:9" s="11" customFormat="1" ht="41.4" x14ac:dyDescent="0.3">
-      <c r="A12" s="41"/>
-      <c r="B12" s="41"/>
-      <c r="C12" s="21" t="s">
-        <v>64</v>
-      </c>
-      <c r="D12" s="22" t="s">
-        <v>58</v>
-      </c>
-      <c r="E12" s="22" t="s">
-        <v>65</v>
-      </c>
-      <c r="F12" s="22" t="s">
-        <v>66</v>
-      </c>
-      <c r="G12" s="22" t="s">
-        <v>67</v>
-      </c>
-      <c r="H12" s="21" t="s">
-        <v>62</v>
-      </c>
-      <c r="I12" s="22"/>
-    </row>
-    <row r="13" spans="1:9" s="11" customFormat="1" ht="41.4" x14ac:dyDescent="0.3">
-      <c r="A13" s="41"/>
-      <c r="B13" s="41"/>
-      <c r="C13" s="21" t="s">
-        <v>68</v>
-      </c>
-      <c r="D13" s="22" t="s">
-        <v>69</v>
-      </c>
-      <c r="E13" s="22" t="s">
-        <v>70</v>
-      </c>
-      <c r="F13" s="22" t="s">
-        <v>71</v>
-      </c>
-      <c r="G13" s="22" t="s">
-        <v>72</v>
-      </c>
-      <c r="H13" s="21" t="s">
-        <v>73</v>
-      </c>
-      <c r="I13" s="22" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="14" spans="1:9" s="11" customFormat="1" ht="41.4" x14ac:dyDescent="0.3">
-      <c r="A14" s="41"/>
-      <c r="B14" s="41"/>
-      <c r="C14" s="21" t="s">
-        <v>75</v>
-      </c>
-      <c r="D14" s="22" t="s">
-        <v>76</v>
-      </c>
-      <c r="E14" s="22" t="s">
-        <v>77</v>
-      </c>
-      <c r="F14" s="22" t="s">
-        <v>78</v>
-      </c>
-      <c r="G14" s="22" t="s">
-        <v>79</v>
-      </c>
-      <c r="H14" s="21" t="s">
-        <v>73</v>
-      </c>
-      <c r="I14" s="22" t="s">
-        <v>80</v>
       </c>
     </row>
     <row r="15" spans="1:9" s="11" customFormat="1" ht="41.4" x14ac:dyDescent="0.3">
       <c r="A15" s="40"/>
       <c r="B15" s="40"/>
-      <c r="C15" s="21" t="s">
+      <c r="C15" s="21">
+        <v>4.4000000000000004</v>
+      </c>
+      <c r="D15" s="22" t="s">
+        <v>63</v>
+      </c>
+      <c r="E15" s="22" t="s">
+        <v>64</v>
+      </c>
+      <c r="F15" s="22" t="s">
+        <v>65</v>
+      </c>
+      <c r="G15" s="22" t="s">
+        <v>66</v>
+      </c>
+      <c r="H15" s="21" t="s">
+        <v>61</v>
+      </c>
+      <c r="I15" s="22" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9" s="11" customFormat="1" ht="41.4" x14ac:dyDescent="0.3">
+      <c r="A16" s="41"/>
+      <c r="B16" s="41"/>
+      <c r="C16" s="21">
+        <v>4.5</v>
+      </c>
+      <c r="D16" s="22" t="s">
+        <v>68</v>
+      </c>
+      <c r="E16" s="22" t="s">
+        <v>69</v>
+      </c>
+      <c r="F16" s="22" t="s">
+        <v>70</v>
+      </c>
+      <c r="G16" s="22" t="s">
+        <v>71</v>
+      </c>
+      <c r="H16" s="21" t="s">
+        <v>72</v>
+      </c>
+      <c r="I16" s="22"/>
+    </row>
+    <row r="17" spans="1:9" s="11" customFormat="1" ht="41.4" x14ac:dyDescent="0.3">
+      <c r="A17" s="46">
+        <v>5</v>
+      </c>
+      <c r="B17" s="46" t="s">
+        <v>73</v>
+      </c>
+      <c r="C17" s="23">
+        <v>5.0999999999999996</v>
+      </c>
+      <c r="D17" s="24" t="s">
+        <v>48</v>
+      </c>
+      <c r="E17" s="24" t="s">
+        <v>74</v>
+      </c>
+      <c r="F17" s="24" t="s">
+        <v>75</v>
+      </c>
+      <c r="G17" s="24" t="s">
+        <v>76</v>
+      </c>
+      <c r="H17" s="23" t="s">
+        <v>77</v>
+      </c>
+      <c r="I17" s="24" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="18" spans="1:9" s="11" customFormat="1" ht="96.6" x14ac:dyDescent="0.3">
+      <c r="A18" s="41"/>
+      <c r="B18" s="41"/>
+      <c r="C18" s="23">
+        <v>5.2</v>
+      </c>
+      <c r="D18" s="24" t="s">
+        <v>48</v>
+      </c>
+      <c r="E18" s="24" t="s">
+        <v>79</v>
+      </c>
+      <c r="F18" s="24" t="s">
+        <v>80</v>
+      </c>
+      <c r="G18" s="24" t="s">
         <v>81</v>
       </c>
-      <c r="D15" s="22" t="s">
+      <c r="H18" s="23" t="s">
+        <v>77</v>
+      </c>
+      <c r="I18" s="24" t="s">
         <v>82</v>
       </c>
-      <c r="E15" s="22" t="s">
+    </row>
+    <row r="19" spans="1:9" s="11" customFormat="1" ht="82.8" x14ac:dyDescent="0.3">
+      <c r="A19" s="39">
+        <v>6</v>
+      </c>
+      <c r="B19" s="39" t="s">
         <v>83</v>
       </c>
-      <c r="F15" s="22" t="s">
+      <c r="C19" s="25">
+        <v>6.1</v>
+      </c>
+      <c r="D19" s="26" t="s">
         <v>84</v>
       </c>
-      <c r="G15" s="22" t="s">
+      <c r="E19" s="26" t="s">
         <v>85</v>
       </c>
-      <c r="H15" s="21" t="s">
+      <c r="F19" s="26" t="s">
         <v>86</v>
       </c>
-      <c r="I15" s="22"/>
-    </row>
-    <row r="16" spans="1:9" s="11" customFormat="1" ht="41.4" x14ac:dyDescent="0.3">
-      <c r="A16" s="46">
-        <v>5</v>
-      </c>
-      <c r="B16" s="46" t="s">
+      <c r="G19" s="26" t="s">
         <v>87</v>
       </c>
-      <c r="C16" s="23" t="s">
+      <c r="H19" s="25" t="s">
         <v>88</v>
       </c>
-      <c r="D16" s="24" t="s">
-        <v>58</v>
-      </c>
-      <c r="E16" s="24" t="s">
+      <c r="I19" s="26" t="s">
         <v>89</v>
       </c>
-      <c r="F16" s="24" t="s">
+    </row>
+    <row r="20" spans="1:9" s="11" customFormat="1" ht="27.6" x14ac:dyDescent="0.3">
+      <c r="A20" s="41"/>
+      <c r="B20" s="41"/>
+      <c r="C20" s="25">
+        <v>6.2</v>
+      </c>
+      <c r="D20" s="26" t="s">
         <v>90</v>
       </c>
-      <c r="G16" s="24" t="s">
+      <c r="E20" s="26" t="s">
         <v>91</v>
       </c>
-      <c r="H16" s="23" t="s">
+      <c r="F20" s="26" t="s">
         <v>92</v>
       </c>
-      <c r="I16" s="24" t="s">
+      <c r="G20" s="26" t="s">
         <v>93</v>
       </c>
-    </row>
-    <row r="17" spans="1:9" s="11" customFormat="1" ht="96.6" x14ac:dyDescent="0.3">
-      <c r="A17" s="40"/>
-      <c r="B17" s="40"/>
-      <c r="C17" s="23" t="s">
+      <c r="H20" s="25" t="s">
+        <v>88</v>
+      </c>
+      <c r="I20" s="26" t="s">
         <v>94</v>
       </c>
-      <c r="D17" s="24" t="s">
-        <v>58</v>
-      </c>
-      <c r="E17" s="24" t="s">
+    </row>
+    <row r="21" spans="1:9" s="11" customFormat="1" ht="41.4" x14ac:dyDescent="0.3">
+      <c r="A21" s="51">
+        <v>7</v>
+      </c>
+      <c r="B21" s="51" t="s">
         <v>95</v>
       </c>
-      <c r="F17" s="24" t="s">
+      <c r="C21" s="37">
+        <v>7.1</v>
+      </c>
+      <c r="D21" s="27" t="s">
+        <v>48</v>
+      </c>
+      <c r="E21" s="27" t="s">
         <v>96</v>
       </c>
-      <c r="G17" s="24" t="s">
+      <c r="F21" s="27" t="s">
         <v>97</v>
       </c>
-      <c r="H17" s="23" t="s">
-        <v>92</v>
-      </c>
-      <c r="I17" s="24" t="s">
+      <c r="G21" s="27" t="s">
         <v>98</v>
       </c>
-    </row>
-    <row r="18" spans="1:9" s="11" customFormat="1" ht="82.8" x14ac:dyDescent="0.3">
-      <c r="A18" s="39">
-        <v>6</v>
-      </c>
-      <c r="B18" s="39" t="s">
+      <c r="H21" s="28" t="s">
         <v>99</v>
       </c>
-      <c r="C18" s="25" t="s">
+      <c r="I21" s="27" t="s">
         <v>100</v>
       </c>
-      <c r="D18" s="26" t="s">
+    </row>
+    <row r="22" spans="1:9" s="11" customFormat="1" ht="41.4" x14ac:dyDescent="0.3">
+      <c r="A22" s="41"/>
+      <c r="B22" s="41"/>
+      <c r="C22" s="37">
+        <v>7.2</v>
+      </c>
+      <c r="D22" s="27" t="s">
+        <v>48</v>
+      </c>
+      <c r="E22" s="27" t="s">
         <v>101</v>
       </c>
-      <c r="E18" s="26" t="s">
+      <c r="F22" s="27" t="s">
         <v>102</v>
       </c>
-      <c r="F18" s="26" t="s">
+      <c r="G22" s="27" t="s">
         <v>103</v>
       </c>
-      <c r="G18" s="26" t="s">
+      <c r="H22" s="28" t="s">
+        <v>99</v>
+      </c>
+      <c r="I22" s="27" t="s">
         <v>104</v>
       </c>
-      <c r="H18" s="25" t="s">
+    </row>
+    <row r="23" spans="1:9" s="11" customFormat="1" ht="82.8" x14ac:dyDescent="0.3">
+      <c r="A23" s="50">
+        <v>8</v>
+      </c>
+      <c r="B23" s="50" t="s">
         <v>105</v>
       </c>
-      <c r="I18" s="26" t="s">
+      <c r="C23" s="38">
+        <v>8.1</v>
+      </c>
+      <c r="D23" s="29" t="s">
         <v>106</v>
       </c>
-    </row>
-    <row r="19" spans="1:9" s="11" customFormat="1" ht="27.6" x14ac:dyDescent="0.3">
-      <c r="A19" s="40"/>
-      <c r="B19" s="40"/>
-      <c r="C19" s="25" t="s">
+      <c r="E23" s="29" t="s">
         <v>107</v>
       </c>
-      <c r="D19" s="26" t="s">
+      <c r="F23" s="29" t="s">
         <v>108</v>
       </c>
-      <c r="E19" s="26" t="s">
+      <c r="G23" s="29" t="s">
         <v>109</v>
       </c>
-      <c r="F19" s="26" t="s">
+      <c r="H23" s="30" t="s">
         <v>110</v>
       </c>
-      <c r="G19" s="26" t="s">
+      <c r="I23" s="29" t="s">
         <v>111</v>
       </c>
-      <c r="H19" s="25" t="s">
-        <v>105</v>
-      </c>
-      <c r="I19" s="26" t="s">
+    </row>
+    <row r="24" spans="1:9" s="11" customFormat="1" ht="82.8" x14ac:dyDescent="0.3">
+      <c r="A24" s="41"/>
+      <c r="B24" s="41"/>
+      <c r="C24" s="38">
+        <v>8.1999999999999993</v>
+      </c>
+      <c r="D24" s="29" t="s">
+        <v>106</v>
+      </c>
+      <c r="E24" s="29" t="s">
         <v>112</v>
       </c>
-    </row>
-    <row r="20" spans="1:9" s="11" customFormat="1" ht="41.4" x14ac:dyDescent="0.3">
-      <c r="A20" s="51">
-        <v>7</v>
-      </c>
-      <c r="B20" s="51" t="s">
+      <c r="F24" s="29" t="s">
         <v>113</v>
       </c>
-      <c r="C20" s="27" t="s">
+      <c r="G24" s="29" t="s">
         <v>114</v>
       </c>
-      <c r="D20" s="28" t="s">
-        <v>58</v>
-      </c>
-      <c r="E20" s="28" t="s">
+      <c r="H24" s="30" t="s">
         <v>115</v>
       </c>
-      <c r="F20" s="28" t="s">
+      <c r="I24" s="29" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="25" spans="1:9" s="11" customFormat="1" ht="41.4" x14ac:dyDescent="0.3">
+      <c r="A25" s="31">
+        <v>9</v>
+      </c>
+      <c r="B25" s="31" t="s">
         <v>116</v>
       </c>
-      <c r="G20" s="28" t="s">
+      <c r="C25" s="32">
+        <v>9.1</v>
+      </c>
+      <c r="D25" s="33" t="s">
+        <v>30</v>
+      </c>
+      <c r="E25" s="33" t="s">
         <v>117</v>
       </c>
-      <c r="H20" s="29" t="s">
+      <c r="F25" s="33" t="s">
         <v>118</v>
       </c>
-      <c r="I20" s="28" t="s">
+      <c r="G25" s="33" t="s">
         <v>119</v>
       </c>
-    </row>
-    <row r="21" spans="1:9" s="11" customFormat="1" ht="41.4" x14ac:dyDescent="0.3">
-      <c r="A21" s="40"/>
-      <c r="B21" s="40"/>
-      <c r="C21" s="27" t="s">
+      <c r="H25" s="32" t="s">
         <v>120</v>
       </c>
-      <c r="D21" s="28" t="s">
-        <v>58</v>
-      </c>
-      <c r="E21" s="28" t="s">
+      <c r="I25" s="33"/>
+    </row>
+    <row r="26" spans="1:9" s="11" customFormat="1" ht="27.6" x14ac:dyDescent="0.3">
+      <c r="A26" s="47">
+        <v>10</v>
+      </c>
+      <c r="B26" s="47" t="s">
         <v>121</v>
       </c>
-      <c r="F21" s="28" t="s">
+      <c r="C26" s="34">
+        <v>10.1</v>
+      </c>
+      <c r="D26" s="35" t="s">
+        <v>48</v>
+      </c>
+      <c r="E26" s="35" t="s">
         <v>122</v>
       </c>
-      <c r="G21" s="28" t="s">
+      <c r="F26" s="35" t="s">
         <v>123</v>
       </c>
-      <c r="H21" s="29" t="s">
-        <v>118</v>
-      </c>
-      <c r="I21" s="28" t="s">
+      <c r="G26" s="35" t="s">
         <v>124</v>
       </c>
-    </row>
-    <row r="22" spans="1:9" s="11" customFormat="1" ht="82.8" x14ac:dyDescent="0.3">
-      <c r="A22" s="50">
-        <v>8</v>
-      </c>
-      <c r="B22" s="50" t="s">
+      <c r="H26" s="34" t="s">
         <v>125</v>
       </c>
-      <c r="C22" s="30" t="s">
-        <v>126</v>
-      </c>
-      <c r="D22" s="31" t="s">
-        <v>127</v>
-      </c>
-      <c r="E22" s="31" t="s">
-        <v>128</v>
-      </c>
-      <c r="F22" s="31" t="s">
-        <v>129</v>
-      </c>
-      <c r="G22" s="31" t="s">
-        <v>130</v>
-      </c>
-      <c r="H22" s="32" t="s">
-        <v>131</v>
-      </c>
-      <c r="I22" s="31" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="23" spans="1:9" s="11" customFormat="1" ht="82.8" x14ac:dyDescent="0.3">
-      <c r="A23" s="40"/>
-      <c r="B23" s="40"/>
-      <c r="C23" s="30" t="s">
-        <v>133</v>
-      </c>
-      <c r="D23" s="31" t="s">
-        <v>127</v>
-      </c>
-      <c r="E23" s="31" t="s">
-        <v>134</v>
-      </c>
-      <c r="F23" s="31" t="s">
-        <v>135</v>
-      </c>
-      <c r="G23" s="31" t="s">
-        <v>136</v>
-      </c>
-      <c r="H23" s="32" t="s">
-        <v>137</v>
-      </c>
-      <c r="I23" s="31" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="24" spans="1:9" s="11" customFormat="1" ht="41.4" x14ac:dyDescent="0.3">
-      <c r="A24" s="33">
-        <v>9</v>
-      </c>
-      <c r="B24" s="33" t="s">
-        <v>138</v>
-      </c>
-      <c r="C24" s="34" t="s">
-        <v>139</v>
-      </c>
-      <c r="D24" s="35" t="s">
-        <v>35</v>
-      </c>
-      <c r="E24" s="35" t="s">
-        <v>140</v>
-      </c>
-      <c r="F24" s="35" t="s">
-        <v>141</v>
-      </c>
-      <c r="G24" s="35" t="s">
-        <v>142</v>
-      </c>
-      <c r="H24" s="34" t="s">
-        <v>143</v>
-      </c>
-      <c r="I24" s="35"/>
-    </row>
-    <row r="25" spans="1:9" s="11" customFormat="1" ht="27.6" x14ac:dyDescent="0.3">
-      <c r="A25" s="47">
-        <v>10</v>
-      </c>
-      <c r="B25" s="47" t="s">
-        <v>144</v>
-      </c>
-      <c r="C25" s="36" t="s">
-        <v>145</v>
-      </c>
-      <c r="D25" s="37" t="s">
-        <v>58</v>
-      </c>
-      <c r="E25" s="37" t="s">
-        <v>146</v>
-      </c>
-      <c r="F25" s="37" t="s">
-        <v>147</v>
-      </c>
-      <c r="G25" s="37" t="s">
-        <v>148</v>
-      </c>
-      <c r="H25" s="36" t="s">
-        <v>149</v>
-      </c>
-      <c r="I25" s="37"/>
-    </row>
-    <row r="26" spans="1:9" s="11" customFormat="1" ht="41.4" x14ac:dyDescent="0.3">
-      <c r="A26" s="41"/>
-      <c r="B26" s="41"/>
-      <c r="C26" s="36" t="s">
-        <v>150</v>
-      </c>
-      <c r="D26" s="37" t="s">
-        <v>151</v>
-      </c>
-      <c r="E26" s="37" t="s">
-        <v>152</v>
-      </c>
-      <c r="F26" s="37" t="s">
-        <v>153</v>
-      </c>
-      <c r="G26" s="37" t="s">
-        <v>154</v>
-      </c>
-      <c r="H26" s="38" t="s">
-        <v>149</v>
-      </c>
-      <c r="I26" s="37"/>
+      <c r="I26" s="35"/>
     </row>
     <row r="27" spans="1:9" s="11" customFormat="1" ht="41.4" x14ac:dyDescent="0.3">
       <c r="A27" s="40"/>
       <c r="B27" s="40"/>
-      <c r="C27" s="36" t="s">
+      <c r="C27" s="34">
+        <v>10.199999999999999</v>
+      </c>
+      <c r="D27" s="35" t="s">
+        <v>126</v>
+      </c>
+      <c r="E27" s="35" t="s">
+        <v>127</v>
+      </c>
+      <c r="F27" s="35" t="s">
+        <v>128</v>
+      </c>
+      <c r="G27" s="35" t="s">
+        <v>129</v>
+      </c>
+      <c r="H27" s="36" t="s">
+        <v>125</v>
+      </c>
+      <c r="I27" s="35"/>
+    </row>
+    <row r="28" spans="1:9" s="11" customFormat="1" ht="41.4" x14ac:dyDescent="0.3">
+      <c r="A28" s="41"/>
+      <c r="B28" s="41"/>
+      <c r="C28" s="34">
+        <v>10.3</v>
+      </c>
+      <c r="D28" s="35" t="s">
+        <v>130</v>
+      </c>
+      <c r="E28" s="35" t="s">
+        <v>131</v>
+      </c>
+      <c r="F28" s="35" t="s">
+        <v>132</v>
+      </c>
+      <c r="G28" s="35" t="s">
+        <v>133</v>
+      </c>
+      <c r="H28" s="34" t="s">
+        <v>125</v>
+      </c>
+      <c r="I28" s="35" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="29" spans="1:9" s="11" customFormat="1" ht="41.4" x14ac:dyDescent="0.3">
+      <c r="A29" s="13">
+        <v>11</v>
+      </c>
+      <c r="B29" s="13" t="s">
+        <v>135</v>
+      </c>
+      <c r="C29" s="14">
+        <v>11.1</v>
+      </c>
+      <c r="D29" s="15" t="s">
+        <v>48</v>
+      </c>
+      <c r="E29" s="15" t="s">
+        <v>136</v>
+      </c>
+      <c r="F29" s="15" t="s">
+        <v>137</v>
+      </c>
+      <c r="G29" s="15" t="s">
+        <v>138</v>
+      </c>
+      <c r="H29" s="14" t="s">
+        <v>139</v>
+      </c>
+      <c r="I29" s="15"/>
+    </row>
+    <row r="30" spans="1:9" s="11" customFormat="1" ht="41.4" x14ac:dyDescent="0.3">
+      <c r="A30" s="16">
+        <v>12</v>
+      </c>
+      <c r="B30" s="16" t="s">
+        <v>140</v>
+      </c>
+      <c r="C30" s="17">
+        <v>12.1</v>
+      </c>
+      <c r="D30" s="18" t="s">
+        <v>48</v>
+      </c>
+      <c r="E30" s="18" t="s">
+        <v>141</v>
+      </c>
+      <c r="F30" s="18" t="s">
+        <v>142</v>
+      </c>
+      <c r="G30" s="18" t="s">
+        <v>143</v>
+      </c>
+      <c r="H30" s="17" t="s">
+        <v>144</v>
+      </c>
+      <c r="I30" s="18"/>
+    </row>
+    <row r="31" spans="1:9" s="11" customFormat="1" ht="55.2" x14ac:dyDescent="0.3">
+      <c r="A31" s="49">
+        <v>13</v>
+      </c>
+      <c r="B31" s="49" t="s">
+        <v>145</v>
+      </c>
+      <c r="C31" s="19">
+        <v>13.1</v>
+      </c>
+      <c r="D31" s="20" t="s">
+        <v>48</v>
+      </c>
+      <c r="E31" s="20" t="s">
+        <v>146</v>
+      </c>
+      <c r="F31" s="20" t="s">
+        <v>147</v>
+      </c>
+      <c r="G31" s="20" t="s">
+        <v>148</v>
+      </c>
+      <c r="H31" s="19" t="s">
+        <v>149</v>
+      </c>
+      <c r="I31" s="20" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="32" spans="1:9" s="11" customFormat="1" ht="55.2" x14ac:dyDescent="0.3">
+      <c r="A32" s="41"/>
+      <c r="B32" s="41"/>
+      <c r="C32" s="19">
+        <v>13.2</v>
+      </c>
+      <c r="D32" s="20" t="s">
+        <v>48</v>
+      </c>
+      <c r="E32" s="20" t="s">
+        <v>151</v>
+      </c>
+      <c r="F32" s="20" t="s">
+        <v>152</v>
+      </c>
+      <c r="G32" s="20" t="s">
+        <v>153</v>
+      </c>
+      <c r="H32" s="19" t="s">
+        <v>149</v>
+      </c>
+      <c r="I32" s="20" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="33" spans="1:9" s="11" customFormat="1" ht="55.2" x14ac:dyDescent="0.3">
+      <c r="A33" s="48">
+        <v>14</v>
+      </c>
+      <c r="B33" s="48" t="s">
+        <v>154</v>
+      </c>
+      <c r="C33" s="21">
+        <v>14.1</v>
+      </c>
+      <c r="D33" s="22" t="s">
+        <v>48</v>
+      </c>
+      <c r="E33" s="22" t="s">
         <v>155</v>
       </c>
-      <c r="D27" s="37" t="s">
+      <c r="F33" s="22" t="s">
         <v>156</v>
       </c>
-      <c r="E27" s="37" t="s">
+      <c r="G33" s="22" t="s">
         <v>157</v>
       </c>
-      <c r="F27" s="37" t="s">
+      <c r="H33" s="21" t="s">
         <v>158</v>
       </c>
-      <c r="G27" s="37" t="s">
+      <c r="I33" s="22" t="s">
         <v>159</v>
       </c>
-      <c r="H27" s="36" t="s">
-        <v>149</v>
-      </c>
-      <c r="I27" s="37" t="s">
+    </row>
+    <row r="34" spans="1:9" s="11" customFormat="1" ht="41.4" x14ac:dyDescent="0.3">
+      <c r="A34" s="40"/>
+      <c r="B34" s="40"/>
+      <c r="C34" s="21">
+        <v>14.2</v>
+      </c>
+      <c r="D34" s="22" t="s">
+        <v>48</v>
+      </c>
+      <c r="E34" s="22" t="s">
         <v>160</v>
       </c>
-    </row>
-    <row r="28" spans="1:9" s="11" customFormat="1" ht="41.4" x14ac:dyDescent="0.3">
-      <c r="A28" s="13">
-        <v>11</v>
-      </c>
-      <c r="B28" s="13" t="s">
+      <c r="F34" s="22" t="s">
         <v>161</v>
       </c>
-      <c r="C28" s="14" t="s">
+      <c r="G34" s="22" t="s">
         <v>162</v>
       </c>
-      <c r="D28" s="15" t="s">
-        <v>58</v>
-      </c>
-      <c r="E28" s="15" t="s">
-        <v>163</v>
-      </c>
-      <c r="F28" s="15" t="s">
-        <v>164</v>
-      </c>
-      <c r="G28" s="15" t="s">
-        <v>165</v>
-      </c>
-      <c r="H28" s="14" t="s">
-        <v>166</v>
-      </c>
-      <c r="I28" s="15"/>
-    </row>
-    <row r="29" spans="1:9" s="11" customFormat="1" ht="41.4" x14ac:dyDescent="0.3">
-      <c r="A29" s="16">
-        <v>12</v>
-      </c>
-      <c r="B29" s="16" t="s">
-        <v>167</v>
-      </c>
-      <c r="C29" s="17" t="s">
-        <v>168</v>
-      </c>
-      <c r="D29" s="18" t="s">
-        <v>58</v>
-      </c>
-      <c r="E29" s="18" t="s">
-        <v>169</v>
-      </c>
-      <c r="F29" s="18" t="s">
-        <v>170</v>
-      </c>
-      <c r="G29" s="18" t="s">
-        <v>171</v>
-      </c>
-      <c r="H29" s="17" t="s">
-        <v>172</v>
-      </c>
-      <c r="I29" s="18"/>
-    </row>
-    <row r="30" spans="1:9" s="11" customFormat="1" ht="55.2" x14ac:dyDescent="0.3">
-      <c r="A30" s="49">
-        <v>13</v>
-      </c>
-      <c r="B30" s="49" t="s">
-        <v>173</v>
-      </c>
-      <c r="C30" s="19" t="s">
-        <v>174</v>
-      </c>
-      <c r="D30" s="20" t="s">
-        <v>58</v>
-      </c>
-      <c r="E30" s="20" t="s">
-        <v>175</v>
-      </c>
-      <c r="F30" s="20" t="s">
-        <v>176</v>
-      </c>
-      <c r="G30" s="20" t="s">
-        <v>177</v>
-      </c>
-      <c r="H30" s="19" t="s">
-        <v>178</v>
-      </c>
-      <c r="I30" s="20" t="s">
-        <v>179</v>
-      </c>
-    </row>
-    <row r="31" spans="1:9" s="11" customFormat="1" ht="55.2" x14ac:dyDescent="0.3">
-      <c r="A31" s="40"/>
-      <c r="B31" s="40"/>
-      <c r="C31" s="19" t="s">
-        <v>180</v>
-      </c>
-      <c r="D31" s="20" t="s">
-        <v>58</v>
-      </c>
-      <c r="E31" s="20" t="s">
-        <v>181</v>
-      </c>
-      <c r="F31" s="20" t="s">
-        <v>182</v>
-      </c>
-      <c r="G31" s="20" t="s">
-        <v>183</v>
-      </c>
-      <c r="H31" s="19" t="s">
-        <v>178</v>
-      </c>
-      <c r="I31" s="20" t="s">
-        <v>179</v>
-      </c>
-    </row>
-    <row r="32" spans="1:9" s="11" customFormat="1" ht="55.2" x14ac:dyDescent="0.3">
-      <c r="A32" s="48">
-        <v>14</v>
-      </c>
-      <c r="B32" s="48" t="s">
-        <v>184</v>
-      </c>
-      <c r="C32" s="21" t="s">
-        <v>185</v>
-      </c>
-      <c r="D32" s="22" t="s">
-        <v>58</v>
-      </c>
-      <c r="E32" s="22" t="s">
-        <v>186</v>
-      </c>
-      <c r="F32" s="22" t="s">
-        <v>187</v>
-      </c>
-      <c r="G32" s="22" t="s">
-        <v>188</v>
-      </c>
-      <c r="H32" s="21" t="s">
-        <v>189</v>
-      </c>
-      <c r="I32" s="22" t="s">
-        <v>190</v>
-      </c>
-    </row>
-    <row r="33" spans="1:9" s="11" customFormat="1" ht="41.4" x14ac:dyDescent="0.3">
-      <c r="A33" s="41"/>
-      <c r="B33" s="41"/>
-      <c r="C33" s="21" t="s">
-        <v>191</v>
-      </c>
-      <c r="D33" s="22" t="s">
-        <v>58</v>
-      </c>
-      <c r="E33" s="22" t="s">
-        <v>192</v>
-      </c>
-      <c r="F33" s="22" t="s">
-        <v>193</v>
-      </c>
-      <c r="G33" s="22" t="s">
-        <v>194</v>
-      </c>
-      <c r="H33" s="21" t="s">
-        <v>189</v>
-      </c>
-      <c r="I33" s="22" t="s">
-        <v>190</v>
-      </c>
-    </row>
-    <row r="34" spans="1:9" s="11" customFormat="1" ht="41.4" x14ac:dyDescent="0.3">
-      <c r="A34" s="41"/>
-      <c r="B34" s="41"/>
-      <c r="C34" s="21" t="s">
-        <v>195</v>
-      </c>
-      <c r="D34" s="22" t="s">
-        <v>196</v>
-      </c>
-      <c r="E34" s="22" t="s">
-        <v>197</v>
-      </c>
-      <c r="F34" s="22" t="s">
-        <v>198</v>
-      </c>
-      <c r="G34" s="22" t="s">
-        <v>199</v>
-      </c>
       <c r="H34" s="21" t="s">
-        <v>200</v>
+        <v>158</v>
       </c>
       <c r="I34" s="22" t="s">
-        <v>201</v>
-      </c>
-    </row>
-    <row r="35" spans="1:9" s="11" customFormat="1" ht="82.8" x14ac:dyDescent="0.3">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="35" spans="1:9" s="11" customFormat="1" ht="41.4" x14ac:dyDescent="0.3">
       <c r="A35" s="40"/>
       <c r="B35" s="40"/>
-      <c r="C35" s="21" t="s">
-        <v>202</v>
+      <c r="C35" s="21">
+        <v>14.3</v>
       </c>
       <c r="D35" s="22" t="s">
-        <v>58</v>
+        <v>163</v>
       </c>
       <c r="E35" s="22" t="s">
-        <v>203</v>
+        <v>164</v>
       </c>
       <c r="F35" s="22" t="s">
-        <v>204</v>
+        <v>165</v>
       </c>
       <c r="G35" s="22" t="s">
-        <v>205</v>
+        <v>166</v>
       </c>
       <c r="H35" s="21" t="s">
+        <v>167</v>
+      </c>
+      <c r="I35" s="22" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="36" spans="1:9" s="11" customFormat="1" ht="82.8" x14ac:dyDescent="0.3">
+      <c r="A36" s="41"/>
+      <c r="B36" s="41"/>
+      <c r="C36" s="21">
+        <v>14.4</v>
+      </c>
+      <c r="D36" s="22" t="s">
+        <v>48</v>
+      </c>
+      <c r="E36" s="22" t="s">
+        <v>169</v>
+      </c>
+      <c r="F36" s="22" t="s">
+        <v>170</v>
+      </c>
+      <c r="G36" s="22" t="s">
+        <v>171</v>
+      </c>
+      <c r="H36" s="21" t="s">
+        <v>158</v>
+      </c>
+      <c r="I36" s="22" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="37" spans="1:9" s="11" customFormat="1" ht="41.4" x14ac:dyDescent="0.3">
+      <c r="A37" s="46">
+        <v>15</v>
+      </c>
+      <c r="B37" s="46" t="s">
+        <v>173</v>
+      </c>
+      <c r="C37" s="23">
+        <v>15.1</v>
+      </c>
+      <c r="D37" s="24" t="s">
+        <v>48</v>
+      </c>
+      <c r="E37" s="24" t="s">
+        <v>174</v>
+      </c>
+      <c r="F37" s="24" t="s">
+        <v>175</v>
+      </c>
+      <c r="G37" s="24" t="s">
+        <v>176</v>
+      </c>
+      <c r="H37" s="23" t="s">
+        <v>177</v>
+      </c>
+      <c r="I37" s="24" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="38" spans="1:9" s="11" customFormat="1" ht="41.4" x14ac:dyDescent="0.3">
+      <c r="A38" s="41"/>
+      <c r="B38" s="41"/>
+      <c r="C38" s="23">
+        <v>15.2</v>
+      </c>
+      <c r="D38" s="24" t="s">
+        <v>48</v>
+      </c>
+      <c r="E38" s="24" t="s">
+        <v>179</v>
+      </c>
+      <c r="F38" s="24" t="s">
+        <v>180</v>
+      </c>
+      <c r="G38" s="24" t="s">
+        <v>181</v>
+      </c>
+      <c r="H38" s="23" t="s">
+        <v>177</v>
+      </c>
+      <c r="I38" s="24" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="39" spans="1:9" s="11" customFormat="1" ht="110.4" x14ac:dyDescent="0.3">
+      <c r="A39" s="39">
+        <v>16</v>
+      </c>
+      <c r="B39" s="39" t="s">
+        <v>182</v>
+      </c>
+      <c r="C39" s="25">
+        <v>16.100000000000001</v>
+      </c>
+      <c r="D39" s="26" t="s">
+        <v>48</v>
+      </c>
+      <c r="E39" s="26" t="s">
+        <v>183</v>
+      </c>
+      <c r="F39" s="26" t="s">
+        <v>184</v>
+      </c>
+      <c r="G39" s="26" t="s">
+        <v>185</v>
+      </c>
+      <c r="H39" s="25" t="s">
+        <v>186</v>
+      </c>
+      <c r="I39" s="26" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="40" spans="1:9" s="11" customFormat="1" ht="55.2" x14ac:dyDescent="0.3">
+      <c r="A40" s="40"/>
+      <c r="B40" s="40"/>
+      <c r="C40" s="25">
+        <v>16.2</v>
+      </c>
+      <c r="D40" s="26" t="s">
+        <v>188</v>
+      </c>
+      <c r="E40" s="26" t="s">
         <v>189</v>
       </c>
-      <c r="I35" s="22" t="s">
-        <v>206</v>
-      </c>
-    </row>
-    <row r="36" spans="1:9" s="11" customFormat="1" ht="41.4" x14ac:dyDescent="0.3">
-      <c r="A36" s="46">
-        <v>15</v>
-      </c>
-      <c r="B36" s="46" t="s">
-        <v>207</v>
-      </c>
-      <c r="C36" s="23" t="s">
-        <v>208</v>
-      </c>
-      <c r="D36" s="24" t="s">
-        <v>58</v>
-      </c>
-      <c r="E36" s="24" t="s">
-        <v>209</v>
-      </c>
-      <c r="F36" s="24" t="s">
-        <v>210</v>
-      </c>
-      <c r="G36" s="24" t="s">
-        <v>211</v>
-      </c>
-      <c r="H36" s="23" t="s">
-        <v>212</v>
-      </c>
-      <c r="I36" s="24" t="s">
-        <v>213</v>
-      </c>
-    </row>
-    <row r="37" spans="1:9" s="11" customFormat="1" ht="41.4" x14ac:dyDescent="0.3">
-      <c r="A37" s="40"/>
-      <c r="B37" s="40"/>
-      <c r="C37" s="23" t="s">
-        <v>214</v>
-      </c>
-      <c r="D37" s="24" t="s">
-        <v>58</v>
-      </c>
-      <c r="E37" s="24" t="s">
-        <v>215</v>
-      </c>
-      <c r="F37" s="24" t="s">
-        <v>216</v>
-      </c>
-      <c r="G37" s="24" t="s">
-        <v>217</v>
-      </c>
-      <c r="H37" s="23" t="s">
-        <v>212</v>
-      </c>
-      <c r="I37" s="24" t="s">
-        <v>213</v>
-      </c>
-    </row>
-    <row r="38" spans="1:9" s="11" customFormat="1" ht="110.4" x14ac:dyDescent="0.3">
-      <c r="A38" s="39">
-        <v>16</v>
-      </c>
-      <c r="B38" s="39" t="s">
-        <v>218</v>
-      </c>
-      <c r="C38" s="25" t="s">
-        <v>219</v>
-      </c>
-      <c r="D38" s="26" t="s">
-        <v>58</v>
-      </c>
-      <c r="E38" s="26" t="s">
-        <v>220</v>
-      </c>
-      <c r="F38" s="26" t="s">
-        <v>221</v>
-      </c>
-      <c r="G38" s="26" t="s">
-        <v>222</v>
-      </c>
-      <c r="H38" s="25" t="s">
-        <v>223</v>
-      </c>
-      <c r="I38" s="26" t="s">
-        <v>224</v>
-      </c>
-    </row>
-    <row r="39" spans="1:9" s="11" customFormat="1" ht="55.2" x14ac:dyDescent="0.3">
-      <c r="A39" s="41"/>
-      <c r="B39" s="41"/>
-      <c r="C39" s="25" t="s">
-        <v>225</v>
-      </c>
-      <c r="D39" s="26" t="s">
-        <v>226</v>
-      </c>
-      <c r="E39" s="26" t="s">
-        <v>227</v>
-      </c>
-      <c r="F39" s="26" t="s">
-        <v>228</v>
-      </c>
-      <c r="G39" s="26" t="s">
-        <v>229</v>
-      </c>
-      <c r="H39" s="25" t="s">
-        <v>223</v>
-      </c>
-      <c r="I39" s="26" t="s">
-        <v>230</v>
-      </c>
-    </row>
-    <row r="40" spans="1:9" s="11" customFormat="1" ht="69" x14ac:dyDescent="0.3">
-      <c r="A40" s="41"/>
-      <c r="B40" s="41"/>
-      <c r="C40" s="25" t="s">
-        <v>231</v>
-      </c>
-      <c r="D40" s="26" t="s">
-        <v>58</v>
-      </c>
-      <c r="E40" s="26" t="s">
-        <v>232</v>
-      </c>
       <c r="F40" s="26" t="s">
-        <v>233</v>
+        <v>190</v>
       </c>
       <c r="G40" s="26" t="s">
-        <v>234</v>
+        <v>191</v>
       </c>
       <c r="H40" s="25" t="s">
-        <v>223</v>
+        <v>186</v>
       </c>
       <c r="I40" s="26" t="s">
-        <v>235</v>
+        <v>192</v>
       </c>
     </row>
     <row r="41" spans="1:9" s="11" customFormat="1" ht="69" x14ac:dyDescent="0.3">
-      <c r="A41" s="41"/>
-      <c r="B41" s="41"/>
-      <c r="C41" s="25" t="s">
-        <v>236</v>
+      <c r="A41" s="40"/>
+      <c r="B41" s="40"/>
+      <c r="C41" s="25">
+        <v>16.3</v>
       </c>
       <c r="D41" s="26" t="s">
-        <v>58</v>
+        <v>48</v>
       </c>
       <c r="E41" s="26" t="s">
-        <v>237</v>
+        <v>193</v>
       </c>
       <c r="F41" s="26" t="s">
-        <v>238</v>
+        <v>194</v>
       </c>
       <c r="G41" s="26" t="s">
-        <v>239</v>
+        <v>195</v>
       </c>
       <c r="H41" s="25" t="s">
-        <v>223</v>
+        <v>186</v>
       </c>
       <c r="I41" s="26" t="s">
-        <v>240</v>
+        <v>196</v>
       </c>
     </row>
     <row r="42" spans="1:9" s="11" customFormat="1" ht="69" x14ac:dyDescent="0.3">
       <c r="A42" s="40"/>
       <c r="B42" s="40"/>
-      <c r="C42" s="25" t="s">
-        <v>241</v>
+      <c r="C42" s="25">
+        <v>16.399999999999999</v>
       </c>
       <c r="D42" s="26" t="s">
-        <v>242</v>
+        <v>48</v>
       </c>
       <c r="E42" s="26" t="s">
-        <v>243</v>
+        <v>197</v>
       </c>
       <c r="F42" s="26" t="s">
-        <v>244</v>
+        <v>198</v>
       </c>
       <c r="G42" s="26" t="s">
-        <v>245</v>
+        <v>199</v>
       </c>
       <c r="H42" s="25" t="s">
-        <v>223</v>
+        <v>186</v>
       </c>
       <c r="I42" s="26" t="s">
-        <v>246</v>
-      </c>
-    </row>
-    <row r="43" spans="1:9" s="11" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="C43" s="5"/>
-      <c r="D43" s="6"/>
-      <c r="E43" s="6"/>
-      <c r="F43" s="6"/>
-      <c r="G43" s="10"/>
-      <c r="H43" s="12"/>
-      <c r="I43" s="6"/>
+        <v>200</v>
+      </c>
+    </row>
+    <row r="43" spans="1:9" s="11" customFormat="1" ht="69" x14ac:dyDescent="0.3">
+      <c r="A43" s="41"/>
+      <c r="B43" s="41"/>
+      <c r="C43" s="25">
+        <v>16.5</v>
+      </c>
+      <c r="D43" s="26" t="s">
+        <v>201</v>
+      </c>
+      <c r="E43" s="26" t="s">
+        <v>202</v>
+      </c>
+      <c r="F43" s="26" t="s">
+        <v>203</v>
+      </c>
+      <c r="G43" s="26" t="s">
+        <v>204</v>
+      </c>
+      <c r="H43" s="25" t="s">
+        <v>186</v>
+      </c>
+      <c r="I43" s="26" t="s">
+        <v>205</v>
+      </c>
     </row>
     <row r="44" spans="1:9" s="11" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A44" s="5"/>
-      <c r="B44" s="5"/>
       <c r="C44" s="5"/>
       <c r="D44" s="6"/>
-      <c r="E44" s="5"/>
+      <c r="E44" s="6"/>
       <c r="F44" s="6"/>
       <c r="G44" s="10"/>
-      <c r="H44" s="5"/>
+      <c r="H44" s="12"/>
       <c r="I44" s="6"/>
     </row>
     <row r="45" spans="1:9" s="11" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A45" s="5"/>
-      <c r="B45" s="6"/>
-      <c r="C45" s="6"/>
+      <c r="B45" s="5"/>
+      <c r="C45" s="5"/>
       <c r="D45" s="6"/>
-      <c r="E45" s="6"/>
+      <c r="E45" s="5"/>
       <c r="F45" s="6"/>
       <c r="G45" s="10"/>
-      <c r="H45" s="12"/>
+      <c r="H45" s="5"/>
       <c r="I45" s="6"/>
     </row>
     <row r="46" spans="1:9" s="11" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A46" s="5"/>
+      <c r="B46" s="6"/>
       <c r="C46" s="6"/>
       <c r="D46" s="6"/>
       <c r="E46" s="6"/>
@@ -2648,7 +2561,6 @@
     </row>
     <row r="48" spans="1:9" s="11" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A48" s="5"/>
-      <c r="B48" s="6"/>
       <c r="C48" s="6"/>
       <c r="D48" s="6"/>
       <c r="E48" s="6"/>
@@ -2658,6 +2570,8 @@
       <c r="I48" s="6"/>
     </row>
     <row r="49" spans="1:9" s="11" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A49" s="5"/>
+      <c r="B49" s="6"/>
       <c r="C49" s="6"/>
       <c r="D49" s="6"/>
       <c r="E49" s="6"/>
@@ -2676,8 +2590,6 @@
       <c r="I50" s="6"/>
     </row>
     <row r="51" spans="1:9" s="11" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A51" s="5"/>
-      <c r="B51" s="6"/>
       <c r="C51" s="6"/>
       <c r="D51" s="6"/>
       <c r="E51" s="6"/>
@@ -2687,6 +2599,8 @@
       <c r="I51" s="6"/>
     </row>
     <row r="52" spans="1:9" s="11" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A52" s="5"/>
+      <c r="B52" s="6"/>
       <c r="C52" s="6"/>
       <c r="D52" s="6"/>
       <c r="E52" s="6"/>
@@ -2696,8 +2610,6 @@
       <c r="I52" s="6"/>
     </row>
     <row r="53" spans="1:9" s="11" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A53" s="5"/>
-      <c r="B53" s="6"/>
       <c r="C53" s="6"/>
       <c r="D53" s="6"/>
       <c r="E53" s="6"/>
@@ -2707,6 +2619,8 @@
       <c r="I53" s="6"/>
     </row>
     <row r="54" spans="1:9" s="11" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A54" s="5"/>
+      <c r="B54" s="6"/>
       <c r="C54" s="6"/>
       <c r="D54" s="6"/>
       <c r="E54" s="6"/>
@@ -2716,8 +2630,6 @@
       <c r="I54" s="6"/>
     </row>
     <row r="55" spans="1:9" s="11" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A55" s="5"/>
-      <c r="B55" s="6"/>
       <c r="C55" s="6"/>
       <c r="D55" s="6"/>
       <c r="E55" s="6"/>
@@ -2727,6 +2639,8 @@
       <c r="I55" s="6"/>
     </row>
     <row r="56" spans="1:9" s="11" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A56" s="5"/>
+      <c r="B56" s="6"/>
       <c r="C56" s="6"/>
       <c r="D56" s="6"/>
       <c r="E56" s="6"/>
@@ -2772,8 +2686,6 @@
       <c r="I60" s="6"/>
     </row>
     <row r="61" spans="1:9" s="11" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A61" s="5"/>
-      <c r="B61" s="6"/>
       <c r="C61" s="6"/>
       <c r="D61" s="6"/>
       <c r="E61" s="6"/>
@@ -2783,6 +2695,8 @@
       <c r="I61" s="6"/>
     </row>
     <row r="62" spans="1:9" s="11" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A62" s="5"/>
+      <c r="B62" s="6"/>
       <c r="C62" s="6"/>
       <c r="D62" s="6"/>
       <c r="E62" s="6"/>
@@ -2791,65 +2705,74 @@
       <c r="H62" s="12"/>
       <c r="I62" s="6"/>
     </row>
-    <row r="63" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="B63" s="3"/>
-      <c r="C63" s="3"/>
-      <c r="E63" s="3"/>
-      <c r="G63" s="4"/>
-      <c r="H63" s="8"/>
+    <row r="63" spans="1:9" s="11" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="C63" s="6"/>
+      <c r="D63" s="6"/>
+      <c r="E63" s="6"/>
+      <c r="F63" s="6"/>
+      <c r="G63" s="10"/>
+      <c r="H63" s="12"/>
+      <c r="I63" s="6"/>
     </row>
     <row r="64" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A64" s="9"/>
+      <c r="B64" s="3"/>
+      <c r="C64" s="3"/>
+      <c r="E64" s="3"/>
       <c r="G64" s="4"/>
-    </row>
-    <row r="65" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="H64" s="8"/>
+    </row>
+    <row r="65" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A65" s="9"/>
-    </row>
-    <row r="66" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="G65" s="4"/>
+    </row>
+    <row r="66" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A66" s="9"/>
     </row>
-    <row r="67" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A67" s="9"/>
     </row>
-    <row r="68" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A68" s="9"/>
     </row>
+    <row r="69" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A69" s="9"/>
+    </row>
   </sheetData>
-  <autoFilter ref="I1:I42" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
+  <autoFilter ref="I1:I43" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
   <mergeCells count="33">
-    <mergeCell ref="B32:B35"/>
-    <mergeCell ref="A30:A31"/>
+    <mergeCell ref="A31:A32"/>
     <mergeCell ref="A1:A2"/>
-    <mergeCell ref="B30:B31"/>
-    <mergeCell ref="A9:A10"/>
-    <mergeCell ref="B22:B23"/>
-    <mergeCell ref="B11:B15"/>
-    <mergeCell ref="A25:A27"/>
-    <mergeCell ref="B16:B17"/>
-    <mergeCell ref="A20:A21"/>
+    <mergeCell ref="B31:B32"/>
+    <mergeCell ref="A9:A11"/>
+    <mergeCell ref="B23:B24"/>
+    <mergeCell ref="B12:B16"/>
+    <mergeCell ref="A26:A28"/>
+    <mergeCell ref="B17:B18"/>
+    <mergeCell ref="A21:A22"/>
     <mergeCell ref="G1:G2"/>
-    <mergeCell ref="A11:A15"/>
-    <mergeCell ref="B20:B21"/>
+    <mergeCell ref="A12:A16"/>
+    <mergeCell ref="B21:B22"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="D1:F1"/>
     <mergeCell ref="B7:B8"/>
     <mergeCell ref="H1:H2"/>
-    <mergeCell ref="B18:B19"/>
-    <mergeCell ref="B38:B42"/>
+    <mergeCell ref="B19:B20"/>
+    <mergeCell ref="B39:B43"/>
     <mergeCell ref="B3:B6"/>
     <mergeCell ref="A7:A8"/>
     <mergeCell ref="C1:C2"/>
-    <mergeCell ref="A36:A37"/>
-    <mergeCell ref="A16:A17"/>
-    <mergeCell ref="A38:A42"/>
+    <mergeCell ref="A37:A38"/>
+    <mergeCell ref="A17:A18"/>
+    <mergeCell ref="A39:A43"/>
     <mergeCell ref="A3:A6"/>
     <mergeCell ref="B1:B2"/>
-    <mergeCell ref="B25:B27"/>
-    <mergeCell ref="A18:A19"/>
-    <mergeCell ref="A32:A35"/>
-    <mergeCell ref="B9:B10"/>
-    <mergeCell ref="A22:A23"/>
-    <mergeCell ref="B36:B37"/>
+    <mergeCell ref="B26:B28"/>
+    <mergeCell ref="A19:A20"/>
+    <mergeCell ref="A33:A36"/>
+    <mergeCell ref="B9:B11"/>
+    <mergeCell ref="A23:A24"/>
+    <mergeCell ref="B37:B38"/>
+    <mergeCell ref="B33:B36"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait"/>
